--- a/data/nissan_raw.xlsx
+++ b/data/nissan_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ottob\Documents\Projects\Data Analytics\ghg-emissions-benchmarking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9190E1-187C-42E6-B747-E4A12B8100FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A278344-58AA-49CD-81DD-7F3E6AE2FBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="129">
   <si>
     <t>company_id</t>
   </si>
@@ -288,9 +288,6 @@
     <t>Restated — see Data Book 2024, p.44: (462 kt-CO₂).</t>
   </si>
   <si>
-    <t>Restated — see Data Book 2023, p.38: (661,241 t-CO₂).</t>
-  </si>
-  <si>
     <t>Only Scope 3 Cat 1 and 11 verified under limited assurance engagement for the year ended March 31, 2025 — see Data Book 2025, p.61.</t>
   </si>
   <si>
@@ -362,25 +359,7 @@
 Nissan does not say whether this figure is market-based or location-based. This project treats it as market-based because Nissan uses emission factors from each electricity supplier or contract — see Data Book 2025, p.62.</t>
   </si>
   <si>
-    <t>Restated — see Data Book 2023, p.38: (1,435,081 t-CO₂). 
-Nissan does not say whether this figure is market-based or location-based. This project treats it as market-based because Nissan uses emission factors from each electricity supplier or contract — see Data Book 2025, p.62.</t>
-  </si>
-  <si>
     <t>Nissan does not say whether its Scope 2 figure is market-based or location-based. This project treats it as market-based because Nissan uses emission factors from each electricity supplier or contract — see Data Book 2025, p.62.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WORKBOOK: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>v1.0, 2026-10-16</t>
-    </r>
   </si>
   <si>
     <r>
@@ -717,9 +696,9 @@
     <t>◦ JPY to USD exchange rate (FY2023)</t>
   </si>
   <si>
-    <t xml:space="preserve">◦ Scope 1 and Scope 2 (FY2023–FY2025), with assurance status and gas-basis notes; 
+    <t>◦ Scope 1 and Scope 2 (FY2023–FY2025), with assurance status and gas-basis notes; 
 ◦ Scope 3 total and categories (FY2025), with assurance status and gas-basis notes; 
-◦ Revenue, headcount and units sold (FY2023–FY2025); </t>
+◦ Revenue, headcount and units sold (FY2023–FY2025)</t>
   </si>
   <si>
     <t>◦ Scope 3 total and categories (FY2024); 
@@ -744,9 +723,6 @@
     </r>
   </si>
   <si>
-    <t>Not republished in Financial Results Summary Sheet FY2024; value taken from the original report.</t>
-  </si>
-  <si>
     <t>Not republished in Data Book 2025; value taken from the original report.</t>
   </si>
   <si>
@@ -754,8 +730,41 @@
 Not verified under limited assurance engagement for the year ended March 31, 2025.</t>
   </si>
   <si>
-    <t>Original value verified under limited assurance engagement for the year ended March 31, 2023 — see Data Book 2023, p.58. 
+    <t>Not restated — see Financial Results Summary Sheet FY2023, p.1.</t>
+  </si>
+  <si>
+    <t>Not republished in Financial Results Summary Sheet FY2024; value taken from Financial Results Summary Sheet FY2023 (prior-year column).</t>
+  </si>
+  <si>
+    <t>Restated — see Data Book 2023, p.38: (661,241 t-CO₂, previous boundary including some equity-method affiliates). 
+Nissan revised its boundary to align with its financial consolidation group and retroactively revised fiscal 2022 figures — see Data Book 2024, p.44, fn.2.</t>
+  </si>
+  <si>
+    <t>Original value not verified under limited assurance engagement for the year ended March 31, 2023; the assured figures in Data Book 2023 cover manufacturing processes only (Scope 1: 579 thousand t-CO₂) — see Data Book 2023, p.38 and p.58. 
 Not verified under limited assurance engagement for the year ended March 31, 2025.</t>
+  </si>
+  <si>
+    <t>Original value not verified under limited assurance engagement for the year ended March 31, 2023; the assured figures in Data Book 2023 cover manufacturing processes only (Scope 2: 1,219 thousand t-CO₂) — see Data Book 2023, p.38 and p.58. 
+Not verified under limited assurance engagement for the year ended March 31, 2025.</t>
+  </si>
+  <si>
+    <t>Restated — see Data Book 2023, p.38: (1,435,081 t-CO₂, previous boundary including some equity-method affiliates). 
+Nissan revised its boundary to align with its financial consolidation group and retroactively revised fiscal 2022 figures — see Data Book 2024, p.44, fn.2. 
+Nissan does not say whether this figure is market-based or location-based. This project treats it as market-based because Nissan uses emission factors from each electricity supplier or contract — see Data Book 2025, p.62.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WORKBOOK: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>v1.0, 2026-10-17</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1487,7 +1496,7 @@
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="13"/>
       <c r="B1" s="27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
@@ -1496,7 +1505,7 @@
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13"/>
       <c r="B2" s="28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -1505,7 +1514,7 @@
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="28" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
@@ -1514,7 +1523,7 @@
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13"/>
       <c r="B4" s="29" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
@@ -1537,7 +1546,7 @@
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15"/>
       <c r="B7" s="17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -1546,7 +1555,7 @@
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15"/>
       <c r="B8" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -1555,7 +1564,7 @@
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15"/>
       <c r="B9" s="25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -1564,7 +1573,7 @@
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15"/>
       <c r="B10" s="25" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
@@ -1573,7 +1582,7 @@
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15"/>
       <c r="B11" s="25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
@@ -1596,7 +1605,7 @@
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="18"/>
       <c r="B14" s="20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -1605,13 +1614,13 @@
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E15" s="18"/>
     </row>
@@ -1621,10 +1630,10 @@
         <v>58</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E16" s="18"/>
     </row>
@@ -1634,10 +1643,10 @@
         <v>60</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E17" s="18"/>
     </row>
@@ -1647,10 +1656,10 @@
         <v>59</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E18" s="18"/>
     </row>
@@ -1660,10 +1669,10 @@
         <v>63</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E19" s="18"/>
     </row>
@@ -1673,10 +1682,10 @@
         <v>64</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E20" s="18"/>
     </row>
@@ -1697,7 +1706,7 @@
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18"/>
       <c r="B23" s="20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -1706,7 +1715,7 @@
     <row r="24" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18"/>
       <c r="B24" s="30" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
@@ -1715,10 +1724,10 @@
     <row r="25" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18"/>
       <c r="B25" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="18"/>
@@ -1726,7 +1735,7 @@
     <row r="26" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="18"/>
       <c r="B26" s="24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
@@ -1866,7 +1875,7 @@
         <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>62</v>
@@ -1965,7 +1974,7 @@
         <v>157</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -1995,7 +2004,7 @@
         <v>157</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2025,7 +2034,7 @@
         <v>157</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -2082,10 +2091,12 @@
       <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="47.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="63" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>61</v>
       </c>
@@ -2141,7 +2152,7 @@
         <v>141</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2171,7 +2182,7 @@
         <v>141</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -2201,7 +2212,7 @@
         <v>141</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -2213,7 +2224,7 @@
         <v>45747</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="9">
         <v>3346</v>
@@ -2241,7 +2252,7 @@
         <v>45382</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" s="9">
         <v>3442</v>
@@ -2259,7 +2270,7 @@
         <v>141</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3"/>
     </row>
@@ -2271,7 +2282,7 @@
         <v>45016</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" s="9">
         <v>3305</v>
@@ -2289,7 +2300,7 @@
         <v>141</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -2339,7 +2350,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>5</v>
@@ -2429,11 +2440,11 @@
         <v>72</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" ht="140.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>61</v>
       </c>
@@ -2465,10 +2476,10 @@
         <v>146</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M4" s="3"/>
     </row>
@@ -2504,7 +2515,7 @@
         <v>26</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -2541,7 +2552,7 @@
         <v>26</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -2578,7 +2589,7 @@
         <v>26</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -2615,7 +2626,7 @@
         <v>146</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>69</v>
@@ -2654,14 +2665,14 @@
         <v>146</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="109.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="187" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
@@ -2693,7 +2704,7 @@
         <v>146</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>126</v>
@@ -2732,10 +2743,10 @@
         <v>149</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M11" s="3"/>
     </row>
@@ -2771,10 +2782,10 @@
         <v>151</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M12" s="3"/>
     </row>
@@ -2810,10 +2821,10 @@
         <v>151</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -2899,7 +2910,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>5</v>
@@ -2952,7 +2963,7 @@
         <v>149</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>69</v>
@@ -2994,7 +3005,7 @@
         <v>151</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>70</v>
@@ -3036,7 +3047,7 @@
         <v>151</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>71</v>
@@ -3079,7 +3090,7 @@
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -3118,10 +3129,10 @@
         <v>151</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -3160,10 +3171,10 @@
         <v>151</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N7" s="3"/>
     </row>
@@ -3203,7 +3214,7 @@
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -3242,10 +3253,10 @@
         <v>151</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N9" s="3"/>
     </row>
@@ -3284,10 +3295,10 @@
         <v>151</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N10" s="3"/>
     </row>
@@ -3327,7 +3338,7 @@
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N11" s="3"/>
     </row>
@@ -3366,10 +3377,10 @@
         <v>151</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N12" s="3"/>
     </row>
@@ -3408,10 +3419,10 @@
         <v>151</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N13" s="3"/>
     </row>
@@ -3451,7 +3462,7 @@
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -3490,10 +3501,10 @@
         <v>151</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N15" s="3"/>
     </row>
@@ -3532,10 +3543,10 @@
         <v>151</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N16" s="3"/>
     </row>
@@ -3575,7 +3586,7 @@
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N17" s="3"/>
     </row>
@@ -3614,10 +3625,10 @@
         <v>151</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N18" s="3"/>
     </row>
@@ -3656,10 +3667,10 @@
         <v>151</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N19" s="3"/>
     </row>
@@ -3699,7 +3710,7 @@
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N20" s="3"/>
     </row>
@@ -3738,10 +3749,10 @@
         <v>151</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N21" s="3"/>
     </row>
@@ -3780,10 +3791,10 @@
         <v>151</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N22" s="3"/>
     </row>
@@ -3822,7 +3833,7 @@
         <v>26</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -3862,10 +3873,10 @@
         <v>151</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N24" s="3"/>
     </row>
@@ -3904,10 +3915,10 @@
         <v>151</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N25" s="3"/>
     </row>
@@ -3947,7 +3958,7 @@
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N26" s="3"/>
     </row>
@@ -3986,10 +3997,10 @@
         <v>151</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N27" s="3"/>
     </row>
@@ -4028,10 +4039,10 @@
         <v>151</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N28" s="3"/>
     </row>
@@ -4071,7 +4082,7 @@
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N29" s="3"/>
     </row>
@@ -4110,10 +4121,10 @@
         <v>151</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N30" s="3"/>
     </row>
@@ -4152,10 +4163,10 @@
         <v>151</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N31" s="3"/>
     </row>
@@ -4194,7 +4205,7 @@
         <v>149</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>69</v>
@@ -4236,7 +4247,7 @@
         <v>151</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>70</v>
@@ -4278,7 +4289,7 @@
         <v>151</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>71</v>
@@ -4321,7 +4332,7 @@
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N35" s="3"/>
     </row>
@@ -4360,10 +4371,10 @@
         <v>151</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N36" s="3"/>
     </row>
@@ -4402,10 +4413,10 @@
         <v>151</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N37" s="3"/>
     </row>
@@ -4445,7 +4456,7 @@
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N38" s="3"/>
     </row>
@@ -4484,10 +4495,10 @@
         <v>151</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N39" s="3"/>
     </row>
@@ -4526,10 +4537,10 @@
         <v>151</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N40" s="3"/>
     </row>
@@ -4568,7 +4579,7 @@
         <v>26</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
@@ -4608,10 +4619,10 @@
         <v>151</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N42" s="3"/>
     </row>
@@ -4650,10 +4661,10 @@
         <v>151</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N43" s="3"/>
     </row>
@@ -4693,7 +4704,7 @@
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N44" s="3"/>
     </row>
@@ -4732,10 +4743,10 @@
         <v>151</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N45" s="3"/>
     </row>
@@ -4774,10 +4785,10 @@
         <v>151</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N46" s="3"/>
     </row>
@@ -4857,7 +4868,7 @@
         <v>1E-3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
